--- a/artfynd/A 12019-2022 artfynd.xlsx
+++ b/artfynd/A 12019-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 12019-2022 artfynd.xlsx
+++ b/artfynd/A 12019-2022 artfynd.xlsx
@@ -675,53 +675,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96282293</v>
+        <v>111011947</v>
       </c>
       <c r="B2" t="n">
-        <v>96254</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223597</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gäddede - Norska gränsen, Jmt</t>
+          <t>Murusjöröset, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>456175.032844714</v>
+        <v>456208</v>
       </c>
       <c r="R2" t="n">
-        <v>7150567.145481641</v>
+        <v>7150456</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,27 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-07-09</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-07-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>North. YS.</t>
+          <t>2023-07-19</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,37 +757,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Charles Campbell</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Indre Cepukaite</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>111011960</v>
       </c>
       <c r="B3" t="n">
-        <v>96674</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99456</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -840,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>456201.8827715188</v>
+        <v>456202</v>
       </c>
       <c r="R3" t="n">
-        <v>7150481.776427494</v>
+        <v>7150481</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -873,19 +848,9 @@
           <t>2023-07-19</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-07-19</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,56 +878,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111011947</v>
+        <v>96282293</v>
       </c>
       <c r="B4" t="n">
-        <v>89401</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99038</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>223597</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Murusjöröset, Jmt</t>
+          <t>Gäddede - Norska gränsen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>456207.5573084637</v>
+        <v>456175</v>
       </c>
       <c r="R4" t="n">
-        <v>7150455.811197293</v>
+        <v>7150567</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,22 +943,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-07-19</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-07-09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-07-19</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-07-09</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>North. YS.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,22 +962,25 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Charles Campbell</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Indre Cepukaite</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 12019-2022 artfynd.xlsx
+++ b/artfynd/A 12019-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111011947</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111011960</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -981,8 +996,18 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96282293</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>